--- a/test-reports/excel/SMARTTABLE_Test_Report.xlsx
+++ b/test-reports/excel/SMARTTABLE_Test_Report.xlsx
@@ -107,7 +107,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>24/8/2026, 5:05:03 pm</t>
+    <t>27/8/2026, 1:33:05 pm</t>
   </si>
   <si>
     <t>Automated Test Run</t>
